--- a/docs/all/idx2_Adultez_loadings_y_tops.xlsx
+++ b/docs/all/idx2_Adultez_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>-0.06778562402479275</v>
+        <v>-0.06778562402479296</v>
       </c>
       <c r="D2">
-        <v>0.03429685937311488</v>
+        <v>0.03429685937311496</v>
       </c>
       <c r="E2">
         <v>3.4</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.04571147423898823</v>
+        <v>0.04571147423898753</v>
       </c>
       <c r="D3">
-        <v>0.02312820787987333</v>
+        <v>0.02312820787987296</v>
       </c>
       <c r="E3">
         <v>2.3</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.5810623274386817</v>
+        <v>-0.5810623274386825</v>
       </c>
       <c r="D4">
-        <v>0.2939946812895071</v>
+        <v>0.2939946812895072</v>
       </c>
       <c r="E4">
         <v>29.4</v>
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.6793163730964967</v>
+        <v>-0.6793163730964972</v>
       </c>
       <c r="D5">
-        <v>0.3437073635174257</v>
+        <v>0.3437073635174256</v>
       </c>
       <c r="E5">
         <v>34.4</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.3808760192753231</v>
+        <v>-0.3808760192753237</v>
       </c>
       <c r="D6">
-        <v>0.1927082837933273</v>
+        <v>0.1927082837933275</v>
       </c>
       <c r="E6">
         <v>19.3</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.2216864116584823</v>
+        <v>0.2216864116584825</v>
       </c>
       <c r="D7">
         <v>0.1121646041467517</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.5408307431833098</v>
+        <v>0.5408307431833088</v>
       </c>
       <c r="D8">
-        <v>0.2509621215941336</v>
+        <v>0.2509621215941329</v>
       </c>
       <c r="E8">
         <v>25.1</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.05248996266043719</v>
+        <v>0.05248996266043826</v>
       </c>
       <c r="D9">
-        <v>0.02435695928475593</v>
+        <v>0.02435695928475641</v>
       </c>
       <c r="E9">
         <v>2.4</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.3855091735178679</v>
+        <v>-0.3855091735178684</v>
       </c>
       <c r="D10">
-        <v>0.1788881296033372</v>
+        <v>0.1788881296033373</v>
       </c>
       <c r="E10">
         <v>17.9</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.1557319495454698</v>
+        <v>-0.1557319495454701</v>
       </c>
       <c r="D11">
-        <v>0.07226442089419997</v>
+        <v>0.07226442089420003</v>
       </c>
       <c r="E11">
         <v>7.2</v>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.4354001382697359</v>
+        <v>0.4354001382697362</v>
       </c>
       <c r="D12">
         <v>0.2020390738133691</v>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.5850674043789553</v>
+        <v>-0.5850674043789559</v>
       </c>
       <c r="D13">
         <v>0.2714892948102043</v>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>-0.4524667359920909</v>
+        <v>-0.4524667359920916</v>
       </c>
       <c r="D14">
-        <v>0.2734576352989371</v>
+        <v>0.2734576352989378</v>
       </c>
       <c r="E14">
         <v>27.3</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>0.8399924509000362</v>
+        <v>0.8399924509000366</v>
       </c>
       <c r="D15">
-        <v>0.5076668206082173</v>
+        <v>0.507666820608218</v>
       </c>
       <c r="E15">
         <v>50.8</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.02201008785333764</v>
+        <v>-0.022010087853337</v>
       </c>
       <c r="D16">
-        <v>0.01330225207362156</v>
+        <v>0.01330225207362118</v>
       </c>
       <c r="E16">
         <v>1.3</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.0006344073445452792</v>
+        <v>-0.0006344073445452929</v>
       </c>
       <c r="D17">
-        <v>0.0003834172071793198</v>
+        <v>0.0003834172071793284</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.0441202359585189</v>
+        <v>0.04412023595851827</v>
       </c>
       <c r="D18">
-        <v>0.02666497763110393</v>
+        <v>0.02666497763110358</v>
       </c>
       <c r="E18">
         <v>2.7</v>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.2953897316945672</v>
+        <v>-0.2953897316945659</v>
       </c>
       <c r="D19">
-        <v>0.1785248971809407</v>
+        <v>0.17852489718094</v>
       </c>
       <c r="E19">
         <v>17.9</v>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.5265145207750164</v>
+        <v>-0.5265145207750151</v>
       </c>
       <c r="D20">
-        <v>0.2568220149017751</v>
+        <v>0.2568220149017743</v>
       </c>
       <c r="E20">
         <v>25.7</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.2470028193825836</v>
+        <v>-0.247002819382582</v>
       </c>
       <c r="D21">
-        <v>0.1204824544380627</v>
+        <v>0.1204824544380619</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.3347703911140005</v>
+        <v>-0.3347703911140008</v>
       </c>
       <c r="D22">
         <v>0.1632935142012755</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.004244715392230509</v>
+        <v>0.004244715392231297</v>
       </c>
       <c r="D23">
-        <v>0.002070477293033749</v>
+        <v>0.002070477293034132</v>
       </c>
       <c r="E23">
         <v>0.2</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.7034746539866523</v>
+        <v>0.703474653986653</v>
       </c>
       <c r="D24">
-        <v>0.3431392125771623</v>
+        <v>0.3431392125771624</v>
       </c>
       <c r="E24">
         <v>34.3</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.2341073374610187</v>
+        <v>0.2341073374610211</v>
       </c>
       <c r="D25">
-        <v>0.1141923265886907</v>
+        <v>0.1141923265886918</v>
       </c>
       <c r="E25">
         <v>11.4</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.4700675787980668</v>
+        <v>0.4700675787980692</v>
       </c>
       <c r="D26">
-        <v>0.2318506078645532</v>
+        <v>0.2318506078645546</v>
       </c>
       <c r="E26">
         <v>23.2</v>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.478076933757329</v>
+        <v>0.4780769337573295</v>
       </c>
       <c r="D27">
-        <v>0.2358010479707526</v>
+        <v>0.235801047970753</v>
       </c>
       <c r="E27">
         <v>23.6</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.0364049067333566</v>
+        <v>-0.03640490673335567</v>
       </c>
       <c r="D28">
-        <v>0.01795592833048159</v>
+        <v>0.01795592833048115</v>
       </c>
       <c r="E28">
         <v>1.8</v>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.08535921631625994</v>
+        <v>0.08535921631625987</v>
       </c>
       <c r="D29">
         <v>0.04210157662940728</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.2745495866908937</v>
+        <v>0.2745495866908911</v>
       </c>
       <c r="D30">
-        <v>0.135415611359554</v>
+        <v>0.1354156113595529</v>
       </c>
       <c r="E30">
         <v>13.5</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.6830006794839831</v>
+        <v>0.6830006794839822</v>
       </c>
       <c r="D31">
-        <v>0.3368752278452513</v>
+        <v>0.3368752278452511</v>
       </c>
       <c r="E31">
         <v>33.7</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="C32">
-        <v>3.261618493709613E-09</v>
+        <v>3.26161845256342E-09</v>
       </c>
       <c r="D32">
-        <v>1.977227822640332E-09</v>
+        <v>1.977227797697071E-09</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>1.754491578514423E-09</v>
+        <v>1.754491447011859E-09</v>
       </c>
       <c r="D33">
-        <v>1.063591456302223E-09</v>
+        <v>1.06359137658397E-09</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.6323513839606231</v>
+        <v>0.6323513839606232</v>
       </c>
       <c r="D34">
         <v>0.3833381348748813</v>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.7120198095855355</v>
+        <v>-0.7120198095855356</v>
       </c>
       <c r="D35">
         <v>0.4316339818708829</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.3052204415842137</v>
+        <v>0.3052204415842139</v>
       </c>
       <c r="D36">
         <v>0.185027878123322</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>-3.447802520455332E-09</v>
+        <v>-3.447802576844625E-09</v>
       </c>
       <c r="D37">
-        <v>2.090094559974211E-09</v>
+        <v>2.090094594158E-09</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3473641732155202</v>
+        <v>0.3473641732155205</v>
       </c>
     </row>
     <row r="3">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2327768034483199</v>
+        <v>0.2327768034483197</v>
       </c>
     </row>
     <row r="4">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.09887768760680676</v>
+        <v>0.09887768760680678</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>9.269775840251347E-17</v>
+        <v>9.269775876742579E-17</v>
       </c>
     </row>
   </sheetData>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.6793163730964967</v>
+        <v>-0.6793163730964972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.5810623274386817</v>
+        <v>-0.5810623274386825</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.3808760192753231</v>
+        <v>-0.3808760192753237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.2216864116584823</v>
+        <v>0.2216864116584825</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.06778562402479275</v>
+        <v>-0.06778562402479296</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.04571147423898823</v>
+        <v>0.04571147423898753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.5850674043789553</v>
+        <v>-0.5850674043789559</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.5408307431833098</v>
+        <v>0.5408307431833088</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.4354001382697359</v>
+        <v>0.4354001382697362</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.3855091735178679</v>
+        <v>-0.3855091735178684</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.1557319495454698</v>
+        <v>-0.1557319495454701</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.05248996266043719</v>
+        <v>0.05248996266043826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
